--- a/pds_admin_chat/Backend/Backend/Data_2.xlsx
+++ b/pds_admin_chat/Backend/Backend/Data_2.xlsx
@@ -113,7 +113,7 @@
     <t>Normal Rice</t>
   </si>
   <si>
-    <t>300.00</t>
+    <t>3174576.00</t>
   </si>
   <si>
     <t>400.00</t>
